--- a/dcf/CGEH.xlsx
+++ b/dcf/CGEH.xlsx
@@ -849,7 +849,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-08</t>
         </is>
       </c>
     </row>
@@ -1130,26 +1130,26 @@
       <c r="A5" s="53" t="n">
         <v>6</v>
       </c>
-      <c r="B5" s="8" t="n">
-        <v>10.67977786314211</v>
-      </c>
-      <c r="C5" s="8" t="n">
-        <v>10.31702863573342</v>
-      </c>
-      <c r="D5" s="8" t="n">
-        <v>9.970205012028202</v>
-      </c>
-      <c r="E5" s="8" t="n">
-        <v>9.638514568676007</v>
-      </c>
-      <c r="F5" s="8" t="n">
-        <v>9.321208266567828</v>
+      <c r="B5" s="54" t="n">
+        <v>8.963296342397104</v>
+      </c>
+      <c r="C5" s="54" t="n">
+        <v>8.669356389464808</v>
+      </c>
+      <c r="D5" s="54" t="n">
+        <v>8.388192360220492</v>
+      </c>
+      <c r="E5" s="54" t="n">
+        <v>8.119171571838082</v>
+      </c>
+      <c r="F5" s="54" t="n">
+        <v>7.861695890980241</v>
       </c>
       <c r="G5" s="54" t="n">
-        <v>9.017577876254949</v>
+        <v>7.615199686640477</v>
       </c>
       <c r="H5" s="54" t="n">
-        <v>8.726953567423049</v>
+        <v>7.379147913305342</v>
       </c>
     </row>
     <row r="6">
@@ -1157,25 +1157,25 @@
         <v>7</v>
       </c>
       <c r="B6" s="8" t="n">
-        <v>11.57111460743402</v>
+        <v>9.669261695277157</v>
       </c>
       <c r="C6" s="8" t="n">
-        <v>11.16897037368659</v>
-      </c>
-      <c r="D6" s="8" t="n">
-        <v>10.78465857229372</v>
-      </c>
-      <c r="E6" s="8" t="n">
-        <v>10.41728653607281</v>
-      </c>
-      <c r="F6" s="8" t="n">
-        <v>10.0660106661749</v>
-      </c>
-      <c r="G6" s="8" t="n">
-        <v>9.73003351192005</v>
-      </c>
-      <c r="H6" s="8" t="n">
-        <v>9.408601037102004</v>
+        <v>9.344119719394788</v>
+      </c>
+      <c r="D6" s="54" t="n">
+        <v>9.033263932507158</v>
+      </c>
+      <c r="E6" s="54" t="n">
+        <v>8.735982255675804</v>
+      </c>
+      <c r="F6" s="54" t="n">
+        <v>8.451601661421948</v>
+      </c>
+      <c r="G6" s="54" t="n">
+        <v>8.179485852856216</v>
+      </c>
+      <c r="H6" s="54" t="n">
+        <v>7.919033090880951</v>
       </c>
     </row>
     <row r="7">
@@ -1183,25 +1183,25 @@
         <v>8</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>12.46245135172592</v>
+        <v>10.37522704815721</v>
       </c>
       <c r="C7" s="8" t="n">
-        <v>12.02091211163976</v>
+        <v>10.01888304932477</v>
       </c>
       <c r="D7" s="8" t="n">
-        <v>11.59911213255923</v>
+        <v>9.678335504793829</v>
       </c>
       <c r="E7" s="8" t="n">
-        <v>11.19605850346962</v>
+        <v>9.352792939513526</v>
       </c>
       <c r="F7" s="8" t="n">
-        <v>10.81081306578198</v>
-      </c>
-      <c r="G7" s="8" t="n">
-        <v>10.44248914758515</v>
-      </c>
-      <c r="H7" s="8" t="n">
-        <v>10.09024850678096</v>
+        <v>9.041507431863657</v>
+      </c>
+      <c r="G7" s="54" t="n">
+        <v>8.743772019071953</v>
+      </c>
+      <c r="H7" s="54" t="n">
+        <v>8.458918268456561</v>
       </c>
     </row>
     <row r="8">
@@ -1209,25 +1209,25 @@
         <v>9</v>
       </c>
       <c r="B8" s="8" t="n">
-        <v>13.35378809601783</v>
+        <v>11.08119240103727</v>
       </c>
       <c r="C8" s="8" t="n">
-        <v>12.87285384959293</v>
+        <v>10.69364637925475</v>
       </c>
       <c r="D8" s="8" t="n">
-        <v>12.41356569282475</v>
+        <v>10.3234070770805</v>
       </c>
       <c r="E8" s="55" t="n">
-        <v>11.97483047086642</v>
+        <v>9.969603623351247</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>11.55561546538905</v>
+        <v>9.631413202305364</v>
       </c>
       <c r="G8" s="8" t="n">
-        <v>11.15494478325026</v>
-      </c>
-      <c r="H8" s="8" t="n">
-        <v>10.77189597645992</v>
+        <v>9.308058185287692</v>
+      </c>
+      <c r="H8" s="54" t="n">
+        <v>8.998803446032168</v>
       </c>
     </row>
     <row r="9">
@@ -1235,25 +1235,25 @@
         <v>10</v>
       </c>
       <c r="B9" s="8" t="n">
-        <v>14.24512484030974</v>
+        <v>11.78715775391732</v>
       </c>
       <c r="C9" s="8" t="n">
-        <v>13.72479558754609</v>
+        <v>11.36840970918473</v>
       </c>
       <c r="D9" s="8" t="n">
-        <v>13.22801925309026</v>
+        <v>10.96847864936717</v>
       </c>
       <c r="E9" s="8" t="n">
-        <v>12.75360243826323</v>
+        <v>10.58641430718897</v>
       </c>
       <c r="F9" s="8" t="n">
-        <v>12.30041786499613</v>
+        <v>10.22131897274707</v>
       </c>
       <c r="G9" s="8" t="n">
-        <v>11.86740041891536</v>
+        <v>9.872344351503427</v>
       </c>
       <c r="H9" s="8" t="n">
-        <v>11.45354344613888</v>
+        <v>9.538688623607776</v>
       </c>
     </row>
     <row r="10">
@@ -1261,25 +1261,25 @@
         <v>11</v>
       </c>
       <c r="B10" s="8" t="n">
-        <v>15.13646158460165</v>
+        <v>12.49312310679738</v>
       </c>
       <c r="C10" s="8" t="n">
-        <v>14.57673732549926</v>
+        <v>12.04317303911471</v>
       </c>
       <c r="D10" s="8" t="n">
-        <v>14.04247281335578</v>
+        <v>11.61355022165383</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>13.53237440566003</v>
+        <v>11.20322499102669</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>13.04522026460321</v>
+        <v>10.81122474318878</v>
       </c>
       <c r="G10" s="8" t="n">
-        <v>12.57985605458046</v>
+        <v>10.43663051771916</v>
       </c>
       <c r="H10" s="8" t="n">
-        <v>12.13519091581783</v>
+        <v>10.07857380118338</v>
       </c>
     </row>
     <row r="11">
@@ -1287,25 +1287,25 @@
         <v>12</v>
       </c>
       <c r="B11" s="8" t="n">
-        <v>16.02779832889355</v>
+        <v>13.19908845967743</v>
       </c>
       <c r="C11" s="8" t="n">
-        <v>15.42867906345243</v>
+        <v>12.71793636904469</v>
       </c>
       <c r="D11" s="8" t="n">
-        <v>14.8569263736213</v>
+        <v>12.2586217939405</v>
       </c>
       <c r="E11" s="8" t="n">
-        <v>14.31114637305684</v>
+        <v>11.82003567486441</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>13.79002266421029</v>
+        <v>11.40113051363048</v>
       </c>
       <c r="G11" s="8" t="n">
-        <v>13.29231169024556</v>
+        <v>11.0009166839349</v>
       </c>
       <c r="H11" s="8" t="n">
-        <v>12.81683838549679</v>
+        <v>10.61845897875899</v>
       </c>
     </row>
     <row r="13">
@@ -1671,7 +1671,7 @@
         </is>
       </c>
       <c r="I8" s="49" t="n">
-        <v>1.318746379166071</v>
+        <v>1.359401386867866</v>
       </c>
       <c r="K8" s="25">
         <f>MAX(-0.05,NORMINV(RAND(),$C$6,$D$6))</f>
@@ -24420,7 +24420,7 @@
         </is>
       </c>
       <c r="B49" s="20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
@@ -24572,13 +24572,13 @@
         </is>
       </c>
       <c r="B58" s="28" t="n">
-        <v>11.97483047086642</v>
+        <v>9.969603623351247</v>
       </c>
       <c r="C58" s="28" t="n">
-        <v>17.75919452492423</v>
+        <v>14.38559020770568</v>
       </c>
       <c r="D58" s="28" t="n">
-        <v>7.833500724024461</v>
+        <v>6.713203926176304</v>
       </c>
     </row>
     <row r="59">
